--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487526_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487526_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.729699999999999</v>
+        <v>6.5682</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9873</v>
+        <v>6.307</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7423</v>
+        <v>0.2612</v>
       </c>
       <c r="G2" t="n">
         <v>2.4833</v>
@@ -610,13 +610,13 @@
         <v>1.7626</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5609</v>
+        <v>1.3995</v>
       </c>
       <c r="T2" t="n">
-        <v>2.936</v>
+        <v>1.2557</v>
       </c>
       <c r="U2" t="n">
-        <v>0.625</v>
+        <v>0.1438</v>
       </c>
       <c r="V2" t="n">
         <v>2.8813</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2497</v>
+        <v>4.8743</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0006</v>
+        <v>6.5717</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7509</v>
+        <v>-1.6974</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1662</v>
@@ -688,13 +688,13 @@
         <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1924</v>
+        <v>-0.5678</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2682</v>
+        <v>0.3029</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9242</v>
+        <v>-0.8707</v>
       </c>
       <c r="V3" t="n">
         <v>3.6498</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8225</v>
+        <v>2.6355</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4025</v>
+        <v>3.1353</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.58</v>
+        <v>-0.4998</v>
       </c>
       <c r="G4" t="n">
         <v>1.6629</v>
@@ -766,13 +766,13 @@
         <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1746</v>
+        <v>-0.3616</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3276</v>
+        <v>0.4052</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.847</v>
+        <v>-0.7668</v>
       </c>
       <c r="V4" t="n">
         <v>0.5507</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0209</v>
+        <v>1.214</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2725</v>
+        <v>1.3319</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2516</v>
+        <v>-0.118</v>
       </c>
       <c r="G5" t="n">
         <v>0.7978</v>
@@ -844,13 +844,13 @@
         <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.6794</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1476</v>
+        <v>0.207</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0201</v>
+        <v>-0.8865</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2754</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6614</v>
+        <v>0.9789</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9391</v>
+        <v>1.2032</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2777</v>
+        <v>-0.2243</v>
       </c>
       <c r="G6" t="n">
         <v>0.881</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8072</v>
+        <v>-0.4896</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4158</v>
+        <v>-0.1517</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3913</v>
+        <v>-0.3379</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1127</v>
+        <v>0.1661</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0594</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1721</v>
+        <v>0.2256</v>
       </c>
       <c r="G7" t="n">
         <v>0.1364</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0238</v>
+        <v>0.0297</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0356</v>
+        <v>0.0891</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0159</v>
+        <v>-0.7845</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9536</v>
+        <v>-0.7489</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0623</v>
+        <v>-0.0356</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4462</v>
@@ -1078,13 +1078,13 @@
         <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0178</v>
+        <v>0.2492</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.2047</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.879</v>
+        <v>-1.0347</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4642</v>
+        <v>-0.0575</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3432</v>
+        <v>-0.9772</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8467</v>
+        <v>0.6505</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2352</v>
+        <v>2.7269</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.0819</v>
+        <v>-2.0764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0334</v>
+        <v>1.7786</v>
       </c>
       <c r="K9" t="n">
-        <v>0.706</v>
+        <v>3.0623</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6726</v>
+        <v>-1.2836</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8801</v>
+        <v>-1.1281</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4708</v>
+        <v>-0.3354</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4093</v>
+        <v>-0.7927</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7834</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>1.068</v>
+        <v>-0.9387</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8973</v>
+        <v>0.1223</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8293</v>
+        <v>-1.061</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
       <c r="W9" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.3756</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0243</v>
+        <v>-2.601</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8333</v>
+        <v>0.662</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.191</v>
+        <v>-3.263</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6505</v>
+        <v>-2.8467</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7269</v>
+        <v>0.2352</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0764</v>
+        <v>-3.0819</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7786</v>
+        <v>0.0334</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0623</v>
+        <v>0.706</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2836</v>
+        <v>-0.6726</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1281</v>
+        <v>-2.8801</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3354</v>
+        <v>-0.4708</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7927</v>
+        <v>-2.4093</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7626</v>
+        <v>2.7419</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9283</v>
+        <v>0.346</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6534</v>
+        <v>1.0951</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2748</v>
+        <v>-0.7491</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5507</v>
+        <v>-2.3756</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7745</v>
+        <v>-3.5196</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5538</v>
+        <v>-1.0851</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2207</v>
+        <v>-2.4345</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0698</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.783</v>
+        <v>-0.5281</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7128</v>
+        <v>-0.2441</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0702</v>
+        <v>-0.2841</v>
       </c>
       <c r="V11" t="n">
         <v>0.6659</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.903199999999998</v>
+        <v>8.497199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6661</v>
+        <v>17.2602</v>
       </c>
       <c r="F12" t="n">
         <v>-8.763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08300000000000018</v>
+        <v>0.08300000000000063</v>
       </c>
       <c r="H12" t="n">
-        <v>9.5306</v>
+        <v>9.530600000000002</v>
       </c>
       <c r="I12" t="n">
         <v>-9.4475</v>
@@ -1390,13 +1390,13 @@
         <v>15.6677</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1351</v>
+        <v>-1.5408</v>
       </c>
       <c r="T12" t="n">
-        <v>2.543699999999999</v>
+        <v>3.1377</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.6785</v>
+        <v>-4.678599999999999</v>
       </c>
       <c r="V12" t="n">
         <v>6.0379</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9947</v>
+        <v>3.4889</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6381</v>
+        <v>3.9451</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6434</v>
+        <v>-0.4562</v>
       </c>
       <c r="G13" t="n">
         <v>3.598</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1006</v>
+        <v>0.5948</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2776</v>
+        <v>0.5846</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.177</v>
+        <v>0.0102</v>
       </c>
       <c r="V13" t="n">
         <v>0.2754</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9663</v>
+        <v>2.4279</v>
       </c>
       <c r="E14" t="n">
-        <v>7.023</v>
+        <v>6.5114</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.0567</v>
+        <v>-4.0835</v>
       </c>
       <c r="G14" t="n">
         <v>1.3224</v>
@@ -1546,13 +1546,13 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3674</v>
+        <v>-0.171</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1204</v>
+        <v>0.6087</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.753</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.4931</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>M. CAMBON DOMINGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2871</v>
+        <v>0.9988</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6294</v>
+        <v>1.0916</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3423</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1813</v>
+        <v>0.1639</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1773</v>
+        <v>-0.5083</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3585</v>
+        <v>0.6722</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0322</v>
+        <v>1.7743</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9918</v>
+        <v>0.4406</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>1.3337</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2135</v>
+        <v>-1.6104</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8145</v>
+        <v>-0.9489</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.399</v>
+        <v>-0.6615</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3917</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4476</v>
+        <v>0.5595</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0257</v>
+        <v>0.0212</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4219</v>
+        <v>0.5383</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6083</v>
+        <v>0.2754</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5507</v>
+        <v>0.2754</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CAMBON DOMINGUEZ</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7368</v>
+        <v>0.722</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3752</v>
+        <v>1.1177</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3616</v>
+        <v>-0.3957</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1639</v>
+        <v>-0.1813</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5083</v>
+        <v>0.1773</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6722</v>
+        <v>-0.3585</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7743</v>
+        <v>1.0322</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4406</v>
+        <v>0.9918</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3337</v>
+        <v>0.0404</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6104</v>
+        <v>-1.2135</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9489</v>
+        <v>-0.8145</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6615</v>
+        <v>-0.399</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2975</v>
+        <v>0.8825</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6952</v>
+        <v>0.514</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9927</v>
+        <v>0.3685</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2754</v>
+        <v>0.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2754</v>
+        <v>0.5507</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4172</v>
+        <v>0.6311</v>
       </c>
       <c r="E17" t="n">
         <v>3.4868</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0696</v>
+        <v>-2.8558</v>
       </c>
       <c r="G17" t="n">
         <v>1.6549</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1962</v>
+        <v>0.0176</v>
       </c>
       <c r="T17" t="n">
         <v>0.2841</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4803</v>
+        <v>-0.2664</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8249</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1739</v>
+        <v>0.2984</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4803</v>
+        <v>-0.2756</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6542</v>
+        <v>0.574</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5031</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2853</v>
+        <v>0.4098</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0418</v>
+        <v>0.1629</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3271</v>
+        <v>0.2469</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4971</v>
+        <v>-0.5772</v>
       </c>
       <c r="E19" t="n">
         <v>-0.801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.304</v>
+        <v>0.2238</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6812</v>
@@ -1936,13 +1936,13 @@
         <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0117</v>
+        <v>-0.0919</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1188</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1071</v>
+        <v>0.0269</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0173</v>
+        <v>-1.7546</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1644</v>
+        <v>-1.0621</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8529</v>
+        <v>-0.6925</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9232</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1724</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7528</v>
+        <v>0.8551</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9253</v>
+        <v>-0.7649</v>
       </c>
       <c r="V20" t="n">
         <v>0.6659</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0923</v>
+        <v>-4.4955</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.527</v>
+        <v>-0.0713</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5653</v>
+        <v>-4.4241</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2461</v>
+        <v>0.3462</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7214</v>
+        <v>-2.9323</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4753</v>
+        <v>3.2784</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9798</v>
+        <v>3.2523</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4799</v>
+        <v>0.1258</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4598</v>
+        <v>3.1264</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2259</v>
+        <v>-2.9061</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.2415</v>
+        <v>-3.0581</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0156</v>
+        <v>0.152</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R21" t="n">
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0144</v>
+        <v>-0.4499</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8203</v>
+        <v>0.5934</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-1.0433</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.8813</v>
+        <v>-2.4332</v>
       </c>
       <c r="W21" t="n">
-        <v>-1.3894</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.492</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3491</v>
+        <v>-4.6027</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4245</v>
+        <v>-2.7315</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9247</v>
+        <v>-1.8712</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6336</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4803</v>
+        <v>0.2267</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.2741</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1008</v>
+        <v>-0.0473</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2166</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5234</v>
+        <v>-5.0401</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9923</v>
+        <v>-2.448</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.5311</v>
+        <v>-2.592</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3462</v>
+        <v>-1.2461</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.9323</v>
+        <v>-2.7214</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2784</v>
+        <v>1.4753</v>
       </c>
       <c r="J23" t="n">
-        <v>3.2523</v>
+        <v>0.9798</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1258</v>
+        <v>-0.4799</v>
       </c>
       <c r="L23" t="n">
-        <v>3.1264</v>
+        <v>1.4598</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.9061</v>
+        <v>-2.2259</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.0581</v>
+        <v>-2.2415</v>
       </c>
       <c r="O23" t="n">
-        <v>0.152</v>
+        <v>0.0156</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R23" t="n">
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4779</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3276</v>
+        <v>0.8993</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1503</v>
+        <v>-0.8326</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4332</v>
+        <v>-2.8813</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.3894</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4332</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9032</v>
+        <v>-7.902999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>8.763</v>
+        <v>8.7631</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.6662</v>
+        <v>-16.666</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.08310000000000001</v>
+        <v>-0.08310000000000017</v>
       </c>
       <c r="H24" t="n">
         <v>-9.5306</v>
@@ -2326,16 +2326,16 @@
         <v>11.7508</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1349</v>
+        <v>2.135</v>
       </c>
       <c r="T24" t="n">
         <v>4.6786</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.5438</v>
+        <v>-2.5434</v>
       </c>
       <c r="V24" t="n">
-        <v>-6.037899999999999</v>
+        <v>-6.0379</v>
       </c>
       <c r="W24" t="n">
         <v>2.6384</v>
